--- a/Team-Data/2012-13/2-27-2012-13.xlsx
+++ b/Team-Data/2012-13/2-27-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F2" t="n">
         <v>23</v>
       </c>
       <c r="G2" t="n">
-        <v>0.589</v>
+        <v>0.582</v>
       </c>
       <c r="H2" t="n">
         <v>48.5</v>
@@ -679,7 +746,7 @@
         <v>37.5</v>
       </c>
       <c r="J2" t="n">
-        <v>80.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="K2" t="n">
         <v>0.463</v>
@@ -688,28 +755,28 @@
         <v>9.1</v>
       </c>
       <c r="M2" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="N2" t="n">
-        <v>0.383</v>
+        <v>0.384</v>
       </c>
       <c r="O2" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="P2" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.706</v>
+        <v>0.704</v>
       </c>
       <c r="R2" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="S2" t="n">
         <v>31.4</v>
       </c>
       <c r="T2" t="n">
-        <v>40.8</v>
+        <v>40.9</v>
       </c>
       <c r="U2" t="n">
         <v>24.4</v>
@@ -727,31 +794,31 @@
         <v>4.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>97.8</v>
+        <v>97.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AD2" t="n">
         <v>23</v>
       </c>
       <c r="AE2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AF2" t="n">
         <v>9</v>
       </c>
       <c r="AG2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH2" t="n">
         <v>9</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>10</v>
       </c>
       <c r="AI2" t="n">
         <v>11</v>
@@ -766,7 +833,7 @@
         <v>3</v>
       </c>
       <c r="AM2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN2" t="n">
         <v>4</v>
@@ -784,7 +851,7 @@
         <v>27</v>
       </c>
       <c r="AS2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT2" t="n">
         <v>26</v>
@@ -793,7 +860,7 @@
         <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AW2" t="n">
         <v>15</v>
@@ -811,7 +878,7 @@
         <v>25</v>
       </c>
       <c r="BB2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BC2" t="n">
         <v>11</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-27-2012-13</t>
+          <t>2013-02-27</t>
         </is>
       </c>
     </row>
@@ -921,16 +988,16 @@
         <v>0.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AE3" t="n">
         <v>15</v>
       </c>
       <c r="AF3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH3" t="n">
         <v>1</v>
@@ -948,25 +1015,25 @@
         <v>25</v>
       </c>
       <c r="AM3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AN3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AP3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR3" t="n">
         <v>28</v>
       </c>
       <c r="AS3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT3" t="n">
         <v>29</v>
@@ -975,7 +1042,7 @@
         <v>7</v>
       </c>
       <c r="AV3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW3" t="n">
         <v>6</v>
@@ -990,7 +1057,7 @@
         <v>27</v>
       </c>
       <c r="BA3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB3" t="n">
         <v>18</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-27-2012-13</t>
+          <t>2013-02-27</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>0.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AE4" t="n">
         <v>8</v>
@@ -1112,7 +1179,7 @@
         <v>10</v>
       </c>
       <c r="AG4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH4" t="n">
         <v>7</v>
@@ -1127,7 +1194,7 @@
         <v>21</v>
       </c>
       <c r="AL4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM4" t="n">
         <v>7</v>
@@ -1136,7 +1203,7 @@
         <v>14</v>
       </c>
       <c r="AO4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP4" t="n">
         <v>9</v>
@@ -1154,10 +1221,10 @@
         <v>15</v>
       </c>
       <c r="AU4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AV4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW4" t="n">
         <v>25</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-27-2012-13</t>
+          <t>2013-02-27</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-9.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AE5" t="n">
         <v>30</v>
@@ -1297,7 +1364,7 @@
         <v>30</v>
       </c>
       <c r="AH5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI5" t="n">
         <v>30</v>
@@ -1327,13 +1394,13 @@
         <v>18</v>
       </c>
       <c r="AR5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS5" t="n">
         <v>26</v>
       </c>
       <c r="AT5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU5" t="n">
         <v>30</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-27-2012-13</t>
+          <t>2013-02-27</t>
         </is>
       </c>
     </row>
@@ -1467,19 +1534,19 @@
         <v>1.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AE6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF6" t="n">
         <v>12</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>11</v>
       </c>
       <c r="AG6" t="n">
         <v>12</v>
       </c>
       <c r="AH6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI6" t="n">
         <v>25</v>
@@ -1503,16 +1570,16 @@
         <v>16</v>
       </c>
       <c r="AP6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR6" t="n">
         <v>6</v>
       </c>
       <c r="AS6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT6" t="n">
         <v>6</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-27-2012-13</t>
+          <t>2013-02-27</t>
         </is>
       </c>
     </row>
@@ -1571,58 +1638,58 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F7" t="n">
         <v>38</v>
       </c>
       <c r="G7" t="n">
-        <v>0.345</v>
+        <v>0.333</v>
       </c>
       <c r="H7" t="n">
         <v>48.2</v>
       </c>
       <c r="I7" t="n">
-        <v>36.6</v>
+        <v>36.7</v>
       </c>
       <c r="J7" t="n">
-        <v>84.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.433</v>
+        <v>0.434</v>
       </c>
       <c r="L7" t="n">
         <v>7.1</v>
       </c>
       <c r="M7" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="N7" t="n">
         <v>0.354</v>
       </c>
       <c r="O7" t="n">
-        <v>17.4</v>
+        <v>17.2</v>
       </c>
       <c r="P7" t="n">
-        <v>22.7</v>
+        <v>22.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.767</v>
+        <v>0.762</v>
       </c>
       <c r="R7" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="S7" t="n">
         <v>28.3</v>
       </c>
       <c r="T7" t="n">
-        <v>40.9</v>
+        <v>41</v>
       </c>
       <c r="U7" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V7" t="n">
         <v>14.1</v>
@@ -1640,37 +1707,37 @@
         <v>21.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>97.8</v>
+        <v>97.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>-3.3</v>
+        <v>-3.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE7" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AF7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AH7" t="n">
         <v>27</v>
       </c>
       <c r="AI7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL7" t="n">
         <v>14</v>
@@ -1679,16 +1746,16 @@
         <v>11</v>
       </c>
       <c r="AN7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO7" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AP7" t="n">
         <v>14</v>
       </c>
       <c r="AQ7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR7" t="n">
         <v>7</v>
@@ -1697,10 +1764,10 @@
         <v>30</v>
       </c>
       <c r="AT7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV7" t="n">
         <v>5</v>
@@ -1709,7 +1776,7 @@
         <v>13</v>
       </c>
       <c r="AX7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AY7" t="n">
         <v>29</v>
@@ -1721,10 +1788,10 @@
         <v>12</v>
       </c>
       <c r="BB7" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BC7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-27-2012-13</t>
+          <t>2013-02-27</t>
         </is>
       </c>
     </row>
@@ -1753,25 +1820,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E8" t="n">
         <v>25</v>
       </c>
       <c r="F8" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G8" t="n">
-        <v>0.439</v>
+        <v>0.446</v>
       </c>
       <c r="H8" t="n">
         <v>48.9</v>
       </c>
       <c r="I8" t="n">
-        <v>38.2</v>
+        <v>38.3</v>
       </c>
       <c r="J8" t="n">
-        <v>84.40000000000001</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="K8" t="n">
         <v>0.453</v>
@@ -1780,10 +1847,10 @@
         <v>7.2</v>
       </c>
       <c r="M8" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0.364</v>
+        <v>0.365</v>
       </c>
       <c r="O8" t="n">
         <v>17.4</v>
@@ -1801,13 +1868,13 @@
         <v>33</v>
       </c>
       <c r="T8" t="n">
-        <v>42.6</v>
+        <v>42.8</v>
       </c>
       <c r="U8" t="n">
         <v>22.8</v>
       </c>
       <c r="V8" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="W8" t="n">
         <v>7.9</v>
@@ -1816,7 +1883,7 @@
         <v>5.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Z8" t="n">
         <v>21</v>
@@ -1825,13 +1892,13 @@
         <v>19.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>101</v>
+        <v>101.3</v>
       </c>
       <c r="AC8" t="n">
-        <v>-1.2</v>
+        <v>-1.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AE8" t="n">
         <v>19</v>
@@ -1846,10 +1913,10 @@
         <v>2</v>
       </c>
       <c r="AI8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK8" t="n">
         <v>11</v>
@@ -1858,13 +1925,13 @@
         <v>13</v>
       </c>
       <c r="AM8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP8" t="n">
         <v>16</v>
@@ -1879,10 +1946,10 @@
         <v>5</v>
       </c>
       <c r="AT8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV8" t="n">
         <v>7</v>
@@ -1891,7 +1958,7 @@
         <v>16</v>
       </c>
       <c r="AX8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AY8" t="n">
         <v>5</v>
@@ -1903,7 +1970,7 @@
         <v>21</v>
       </c>
       <c r="BB8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC8" t="n">
         <v>18</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-27-2012-13</t>
+          <t>2013-02-27</t>
         </is>
       </c>
     </row>
@@ -1935,28 +2002,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E9" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F9" t="n">
         <v>22</v>
       </c>
       <c r="G9" t="n">
-        <v>0.627</v>
+        <v>0.621</v>
       </c>
       <c r="H9" t="n">
         <v>48.6</v>
       </c>
       <c r="I9" t="n">
-        <v>40.5</v>
+        <v>40.4</v>
       </c>
       <c r="J9" t="n">
-        <v>85.3</v>
+        <v>85.2</v>
       </c>
       <c r="K9" t="n">
-        <v>0.475</v>
+        <v>0.474</v>
       </c>
       <c r="L9" t="n">
         <v>6.5</v>
@@ -1965,55 +2032,55 @@
         <v>19.1</v>
       </c>
       <c r="N9" t="n">
-        <v>0.339</v>
+        <v>0.341</v>
       </c>
       <c r="O9" t="n">
         <v>18.1</v>
       </c>
       <c r="P9" t="n">
-        <v>26.3</v>
+        <v>26.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="R9" t="n">
         <v>13.5</v>
       </c>
       <c r="S9" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T9" t="n">
-        <v>45.1</v>
+        <v>45.2</v>
       </c>
       <c r="U9" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="V9" t="n">
         <v>15.2</v>
       </c>
       <c r="W9" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="X9" t="n">
         <v>6.6</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="Z9" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AA9" t="n">
         <v>22</v>
       </c>
       <c r="AB9" t="n">
-        <v>105.5</v>
+        <v>105.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE9" t="n">
         <v>6</v>
@@ -2025,7 +2092,7 @@
         <v>8</v>
       </c>
       <c r="AH9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI9" t="n">
         <v>1</v>
@@ -2034,16 +2101,16 @@
         <v>2</v>
       </c>
       <c r="AK9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM9" t="n">
         <v>16</v>
       </c>
       <c r="AN9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO9" t="n">
         <v>7</v>
@@ -2052,7 +2119,7 @@
         <v>3</v>
       </c>
       <c r="AQ9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AR9" t="n">
         <v>1</v>
@@ -2067,10 +2134,10 @@
         <v>3</v>
       </c>
       <c r="AV9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX9" t="n">
         <v>4</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-27-2012-13</t>
+          <t>2013-02-27</t>
         </is>
       </c>
     </row>
@@ -2117,28 +2184,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F10" t="n">
         <v>37</v>
       </c>
       <c r="G10" t="n">
-        <v>0.383</v>
+        <v>0.373</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
       </c>
       <c r="I10" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J10" t="n">
-        <v>81.40000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.446</v>
+        <v>0.444</v>
       </c>
       <c r="L10" t="n">
         <v>6.1</v>
@@ -2147,31 +2214,31 @@
         <v>16.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0.363</v>
+        <v>0.359</v>
       </c>
       <c r="O10" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="P10" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.695</v>
+        <v>0.696</v>
       </c>
       <c r="R10" t="n">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
       <c r="S10" t="n">
         <v>30.8</v>
       </c>
       <c r="T10" t="n">
-        <v>43.2</v>
+        <v>43.3</v>
       </c>
       <c r="U10" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="V10" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W10" t="n">
         <v>6.9</v>
@@ -2183,10 +2250,10 @@
         <v>5.6</v>
       </c>
       <c r="Z10" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AA10" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AB10" t="n">
         <v>94.90000000000001</v>
@@ -2198,7 +2265,7 @@
         <v>1</v>
       </c>
       <c r="AE10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF10" t="n">
         <v>23</v>
@@ -2207,13 +2274,13 @@
         <v>22</v>
       </c>
       <c r="AH10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>18</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>19</v>
       </c>
       <c r="AK10" t="n">
         <v>15</v>
@@ -2222,13 +2289,13 @@
         <v>23</v>
       </c>
       <c r="AM10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AN10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AO10" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AP10" t="n">
         <v>10</v>
@@ -2240,28 +2307,28 @@
         <v>9</v>
       </c>
       <c r="AS10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU10" t="n">
         <v>24</v>
       </c>
       <c r="AV10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW10" t="n">
         <v>27</v>
       </c>
       <c r="AX10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-27-2012-13</t>
+          <t>2013-02-27</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E11" t="n">
         <v>33</v>
       </c>
       <c r="F11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G11" t="n">
-        <v>0.569</v>
+        <v>0.579</v>
       </c>
       <c r="H11" t="n">
         <v>48.4</v>
@@ -2317,19 +2384,19 @@
         <v>38</v>
       </c>
       <c r="J11" t="n">
-        <v>83.2</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L11" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="M11" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="N11" t="n">
-        <v>0.398</v>
+        <v>0.394</v>
       </c>
       <c r="O11" t="n">
         <v>17.3</v>
@@ -2338,22 +2405,22 @@
         <v>21.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.799</v>
+        <v>0.798</v>
       </c>
       <c r="R11" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="S11" t="n">
         <v>33.8</v>
       </c>
       <c r="T11" t="n">
-        <v>44.8</v>
+        <v>44.9</v>
       </c>
       <c r="U11" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="V11" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="W11" t="n">
         <v>6.8</v>
@@ -2362,58 +2429,58 @@
         <v>4.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>101.2</v>
+        <v>101.1</v>
       </c>
       <c r="AC11" t="n">
         <v>-0.4</v>
       </c>
       <c r="AD11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE11" t="n">
         <v>9</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AF11" t="n">
         <v>10</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>11</v>
       </c>
       <c r="AG11" t="n">
         <v>11</v>
       </c>
       <c r="AH11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI11" t="n">
         <v>8</v>
       </c>
       <c r="AJ11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AK11" t="n">
         <v>10</v>
       </c>
       <c r="AL11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN11" t="n">
         <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP11" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AQ11" t="n">
         <v>2</v>
@@ -2431,7 +2498,7 @@
         <v>11</v>
       </c>
       <c r="AV11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW11" t="n">
         <v>28</v>
@@ -2449,7 +2516,7 @@
         <v>22</v>
       </c>
       <c r="BB11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC11" t="n">
         <v>15</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-27-2012-13</t>
+          <t>2013-02-27</t>
         </is>
       </c>
     </row>
@@ -2481,46 +2548,46 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E12" t="n">
         <v>31</v>
       </c>
       <c r="F12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G12" t="n">
-        <v>0.525</v>
+        <v>0.534</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
       </c>
       <c r="I12" t="n">
-        <v>38.6</v>
+        <v>38.5</v>
       </c>
       <c r="J12" t="n">
-        <v>83.3</v>
+        <v>83.2</v>
       </c>
       <c r="K12" t="n">
         <v>0.463</v>
       </c>
       <c r="L12" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="M12" t="n">
-        <v>28.6</v>
+        <v>28.7</v>
       </c>
       <c r="N12" t="n">
-        <v>0.367</v>
+        <v>0.368</v>
       </c>
       <c r="O12" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="P12" t="n">
         <v>24.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.754</v>
+        <v>0.756</v>
       </c>
       <c r="R12" t="n">
         <v>10.9</v>
@@ -2529,16 +2596,16 @@
         <v>32.1</v>
       </c>
       <c r="T12" t="n">
-        <v>43</v>
+        <v>42.9</v>
       </c>
       <c r="U12" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="V12" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="W12" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="X12" t="n">
         <v>4.1</v>
@@ -2550,25 +2617,25 @@
         <v>20.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>106.4</v>
+        <v>106.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE12" t="n">
         <v>13</v>
       </c>
       <c r="AF12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH12" t="n">
         <v>25</v>
@@ -2577,7 +2644,7 @@
         <v>4</v>
       </c>
       <c r="AJ12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK12" t="n">
         <v>6</v>
@@ -2598,7 +2665,7 @@
         <v>6</v>
       </c>
       <c r="AQ12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR12" t="n">
         <v>20</v>
@@ -2616,7 +2683,7 @@
         <v>30</v>
       </c>
       <c r="AW12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX12" t="n">
         <v>28</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-27-2012-13</t>
+          <t>2013-02-27</t>
         </is>
       </c>
     </row>
@@ -2741,10 +2808,10 @@
         <v>4.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AE13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF13" t="n">
         <v>7</v>
@@ -2753,7 +2820,7 @@
         <v>6</v>
       </c>
       <c r="AH13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI13" t="n">
         <v>28</v>
@@ -2762,16 +2829,16 @@
         <v>23</v>
       </c>
       <c r="AK13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM13" t="n">
         <v>15</v>
       </c>
       <c r="AN13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO13" t="n">
         <v>17</v>
@@ -2792,10 +2859,10 @@
         <v>1</v>
       </c>
       <c r="AU13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW13" t="n">
         <v>24</v>
@@ -2804,7 +2871,7 @@
         <v>3</v>
       </c>
       <c r="AY13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ13" t="n">
         <v>16</v>
@@ -2813,7 +2880,7 @@
         <v>5</v>
       </c>
       <c r="BB13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC13" t="n">
         <v>5</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-27-2012-13</t>
+          <t>2013-02-27</t>
         </is>
       </c>
     </row>
@@ -2923,10 +2990,10 @@
         <v>6.6</v>
       </c>
       <c r="AD14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE14" t="n">
         <v>2</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>3</v>
       </c>
       <c r="AF14" t="n">
         <v>4</v>
@@ -2944,7 +3011,7 @@
         <v>26</v>
       </c>
       <c r="AK14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL14" t="n">
         <v>12</v>
@@ -2953,7 +3020,7 @@
         <v>10</v>
       </c>
       <c r="AN14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO14" t="n">
         <v>18</v>
@@ -2968,7 +3035,7 @@
         <v>13</v>
       </c>
       <c r="AS14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT14" t="n">
         <v>17</v>
@@ -2989,7 +3056,7 @@
         <v>6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA14" t="n">
         <v>7</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-27-2012-13</t>
+          <t>2013-02-27</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>0.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AE15" t="n">
         <v>16</v>
@@ -3144,19 +3211,19 @@
         <v>1</v>
       </c>
       <c r="AQ15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AR15" t="n">
         <v>12</v>
       </c>
       <c r="AS15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT15" t="n">
         <v>4</v>
       </c>
       <c r="AU15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV15" t="n">
         <v>27</v>
@@ -3165,7 +3232,7 @@
         <v>21</v>
       </c>
       <c r="AX15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY15" t="n">
         <v>15</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-27-2012-13</t>
+          <t>2013-02-27</t>
         </is>
       </c>
     </row>
@@ -3209,28 +3276,28 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E16" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F16" t="n">
         <v>18</v>
       </c>
       <c r="G16" t="n">
-        <v>0.679</v>
+        <v>0.673</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
       </c>
       <c r="I16" t="n">
-        <v>36.1</v>
+        <v>36.3</v>
       </c>
       <c r="J16" t="n">
-        <v>82.2</v>
+        <v>82.3</v>
       </c>
       <c r="K16" t="n">
-        <v>0.44</v>
+        <v>0.441</v>
       </c>
       <c r="L16" t="n">
         <v>4.7</v>
@@ -3242,22 +3309,22 @@
         <v>0.343</v>
       </c>
       <c r="O16" t="n">
-        <v>16.4</v>
+        <v>16.2</v>
       </c>
       <c r="P16" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.782</v>
+        <v>0.781</v>
       </c>
       <c r="R16" t="n">
         <v>13.4</v>
       </c>
       <c r="S16" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="T16" t="n">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
       <c r="U16" t="n">
         <v>21</v>
@@ -3269,10 +3336,10 @@
         <v>8.9</v>
       </c>
       <c r="X16" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Z16" t="n">
         <v>19.8</v>
@@ -3281,7 +3348,7 @@
         <v>19.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>93.3</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="AC16" t="n">
         <v>3.8</v>
@@ -3299,16 +3366,16 @@
         <v>5</v>
       </c>
       <c r="AH16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AJ16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK16" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AL16" t="n">
         <v>30</v>
@@ -3317,16 +3384,16 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO16" t="n">
         <v>23</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>22</v>
       </c>
       <c r="AP16" t="n">
         <v>24</v>
       </c>
       <c r="AQ16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR16" t="n">
         <v>2</v>
@@ -3344,25 +3411,25 @@
         <v>14</v>
       </c>
       <c r="AW16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY16" t="n">
         <v>21</v>
       </c>
       <c r="AZ16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA16" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BB16" t="n">
         <v>27</v>
       </c>
       <c r="BC16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-27-2012-13</t>
+          <t>2013-02-27</t>
         </is>
       </c>
     </row>
@@ -3469,13 +3536,13 @@
         <v>7.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AE17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG17" t="n">
         <v>2</v>
@@ -3502,13 +3569,13 @@
         <v>3</v>
       </c>
       <c r="AO17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP17" t="n">
         <v>12</v>
       </c>
       <c r="AQ17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR17" t="n">
         <v>29</v>
@@ -3538,7 +3605,7 @@
         <v>12</v>
       </c>
       <c r="BA17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BB17" t="n">
         <v>5</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-27-2012-13</t>
+          <t>2013-02-27</t>
         </is>
       </c>
     </row>
@@ -3573,34 +3640,34 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F18" t="n">
         <v>28</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5</v>
+        <v>0.491</v>
       </c>
       <c r="H18" t="n">
         <v>48.3</v>
       </c>
       <c r="I18" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="J18" t="n">
         <v>86.90000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>0.435</v>
+        <v>0.434</v>
       </c>
       <c r="L18" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M18" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="N18" t="n">
         <v>0.349</v>
@@ -3615,10 +3682,10 @@
         <v>0.733</v>
       </c>
       <c r="R18" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="S18" t="n">
-        <v>30.8</v>
+        <v>30.7</v>
       </c>
       <c r="T18" t="n">
         <v>43.7</v>
@@ -3639,43 +3706,43 @@
         <v>4.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="AA18" t="n">
         <v>19.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>97.90000000000001</v>
+        <v>97.7</v>
       </c>
       <c r="AC18" t="n">
-        <v>-0.9</v>
+        <v>-1</v>
       </c>
       <c r="AD18" t="n">
         <v>23</v>
       </c>
       <c r="AE18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF18" t="n">
         <v>16</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>15</v>
       </c>
       <c r="AG18" t="n">
         <v>16</v>
       </c>
       <c r="AH18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ18" t="n">
         <v>1</v>
       </c>
       <c r="AK18" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AL18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM18" t="n">
         <v>20</v>
@@ -3687,7 +3754,7 @@
         <v>24</v>
       </c>
       <c r="AP18" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AQ18" t="n">
         <v>24</v>
@@ -3696,7 +3763,7 @@
         <v>3</v>
       </c>
       <c r="AS18" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AT18" t="n">
         <v>5</v>
@@ -3723,7 +3790,7 @@
         <v>19</v>
       </c>
       <c r="BB18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC18" t="n">
         <v>17</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-27-2012-13</t>
+          <t>2013-02-27</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3918,7 @@
         <v>26</v>
       </c>
       <c r="AJ19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK19" t="n">
         <v>25</v>
@@ -3884,7 +3951,7 @@
         <v>7</v>
       </c>
       <c r="AU19" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AV19" t="n">
         <v>26</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-27-2012-13</t>
+          <t>2013-02-27</t>
         </is>
       </c>
     </row>
@@ -3937,37 +4004,37 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E20" t="n">
         <v>20</v>
       </c>
       <c r="F20" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G20" t="n">
-        <v>0.339</v>
+        <v>0.345</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
       </c>
       <c r="I20" t="n">
-        <v>36.3</v>
+        <v>36.4</v>
       </c>
       <c r="J20" t="n">
         <v>80.40000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.451</v>
+        <v>0.453</v>
       </c>
       <c r="L20" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="M20" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="N20" t="n">
-        <v>0.371</v>
+        <v>0.373</v>
       </c>
       <c r="O20" t="n">
         <v>14.8</v>
@@ -3976,58 +4043,58 @@
         <v>19.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.77</v>
+        <v>0.769</v>
       </c>
       <c r="R20" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="S20" t="n">
-        <v>29.8</v>
+        <v>30</v>
       </c>
       <c r="T20" t="n">
-        <v>41.1</v>
+        <v>41.3</v>
       </c>
       <c r="U20" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="V20" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W20" t="n">
         <v>6.4</v>
       </c>
       <c r="X20" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y20" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="Z20" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AA20" t="n">
         <v>18.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>94.2</v>
+        <v>94.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>-3.6</v>
+        <v>-2.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE20" t="n">
         <v>23</v>
       </c>
       <c r="AF20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI20" t="n">
         <v>20</v>
@@ -4036,7 +4103,7 @@
         <v>27</v>
       </c>
       <c r="AK20" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AL20" t="n">
         <v>17</v>
@@ -4054,16 +4121,16 @@
         <v>28</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS20" t="n">
         <v>23</v>
       </c>
       <c r="AT20" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AU20" t="n">
         <v>21</v>
@@ -4081,16 +4148,16 @@
         <v>25</v>
       </c>
       <c r="AZ20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA20" t="n">
         <v>27</v>
       </c>
       <c r="BB20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC20" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-27-2012-13</t>
+          <t>2013-02-27</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E21" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F21" t="n">
         <v>20</v>
       </c>
       <c r="G21" t="n">
-        <v>0.63</v>
+        <v>0.623</v>
       </c>
       <c r="H21" t="n">
         <v>48.1</v>
@@ -4140,43 +4207,43 @@
         <v>82.40000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>0.442</v>
+        <v>0.443</v>
       </c>
       <c r="L21" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="M21" t="n">
-        <v>29.1</v>
+        <v>29</v>
       </c>
       <c r="N21" t="n">
-        <v>0.373</v>
+        <v>0.374</v>
       </c>
       <c r="O21" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="P21" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
       <c r="R21" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="S21" t="n">
         <v>30</v>
       </c>
       <c r="T21" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="U21" t="n">
         <v>19.6</v>
       </c>
       <c r="V21" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="W21" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="X21" t="n">
         <v>3.8</v>
@@ -4191,16 +4258,16 @@
         <v>19.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>100.3</v>
+        <v>100.1</v>
       </c>
       <c r="AC21" t="n">
         <v>3.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF21" t="n">
         <v>6</v>
@@ -4230,22 +4297,22 @@
         <v>6</v>
       </c>
       <c r="AO21" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AP21" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AQ21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS21" t="n">
         <v>22</v>
       </c>
       <c r="AT21" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AU21" t="n">
         <v>29</v>
@@ -4257,7 +4324,7 @@
         <v>14</v>
       </c>
       <c r="AX21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AY21" t="n">
         <v>2</v>
@@ -4272,7 +4339,7 @@
         <v>10</v>
       </c>
       <c r="BC21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-27-2012-13</t>
+          <t>2013-02-27</t>
         </is>
       </c>
     </row>
@@ -4301,85 +4368,85 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E22" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F22" t="n">
         <v>15</v>
       </c>
       <c r="G22" t="n">
-        <v>0.737</v>
+        <v>0.732</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
       </c>
       <c r="I22" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="J22" t="n">
-        <v>79.2</v>
+        <v>79.3</v>
       </c>
       <c r="K22" t="n">
-        <v>0.484</v>
+        <v>0.483</v>
       </c>
       <c r="L22" t="n">
         <v>7.6</v>
       </c>
       <c r="M22" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="N22" t="n">
-        <v>0.393</v>
+        <v>0.392</v>
       </c>
       <c r="O22" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="P22" t="n">
         <v>26.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.836</v>
+        <v>0.833</v>
       </c>
       <c r="R22" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="S22" t="n">
-        <v>32.8</v>
+        <v>32.7</v>
       </c>
       <c r="T22" t="n">
-        <v>43</v>
+        <v>42.9</v>
       </c>
       <c r="U22" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="V22" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="W22" t="n">
         <v>8.4</v>
       </c>
       <c r="X22" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="Y22" t="n">
         <v>4.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AA22" t="n">
         <v>21</v>
       </c>
       <c r="AB22" t="n">
-        <v>106.8</v>
+        <v>106.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4394,7 +4461,7 @@
         <v>14</v>
       </c>
       <c r="AI22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ22" t="n">
         <v>29</v>
@@ -4430,13 +4497,13 @@
         <v>10</v>
       </c>
       <c r="AU22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV22" t="n">
         <v>29</v>
       </c>
       <c r="AW22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX22" t="n">
         <v>1</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-27-2012-13</t>
+          <t>2013-02-27</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E23" t="n">
         <v>16</v>
       </c>
       <c r="F23" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G23" t="n">
-        <v>0.276</v>
+        <v>0.281</v>
       </c>
       <c r="H23" t="n">
         <v>48.3</v>
@@ -4516,22 +4583,22 @@
         <v>0.337</v>
       </c>
       <c r="O23" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="P23" t="n">
-        <v>16</v>
+        <v>15.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.767</v>
+        <v>0.765</v>
       </c>
       <c r="R23" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="S23" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="T23" t="n">
-        <v>42.7</v>
+        <v>42.8</v>
       </c>
       <c r="U23" t="n">
         <v>23.4</v>
@@ -4543,25 +4610,25 @@
         <v>5.9</v>
       </c>
       <c r="X23" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y23" t="n">
         <v>4.9</v>
       </c>
       <c r="Z23" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>94</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.9</v>
+        <v>-5.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE23" t="n">
         <v>29</v>
@@ -4576,13 +4643,13 @@
         <v>24</v>
       </c>
       <c r="AI23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL23" t="n">
         <v>21</v>
@@ -4594,13 +4661,13 @@
         <v>28</v>
       </c>
       <c r="AO23" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AP23" t="n">
         <v>30</v>
       </c>
       <c r="AQ23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR23" t="n">
         <v>24</v>
@@ -4609,13 +4676,13 @@
         <v>8</v>
       </c>
       <c r="AT23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU23" t="n">
         <v>5</v>
       </c>
       <c r="AV23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW23" t="n">
         <v>30</v>
@@ -4633,7 +4700,7 @@
         <v>30</v>
       </c>
       <c r="BB23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC23" t="n">
         <v>28</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-27-2012-13</t>
+          <t>2013-02-27</t>
         </is>
       </c>
     </row>
@@ -4743,16 +4810,16 @@
         <v>-3.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AE24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF24" t="n">
         <v>20</v>
       </c>
       <c r="AG24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH24" t="n">
         <v>22</v>
@@ -4773,10 +4840,10 @@
         <v>23</v>
       </c>
       <c r="AN24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP24" t="n">
         <v>29</v>
@@ -4794,7 +4861,7 @@
         <v>21</v>
       </c>
       <c r="AU24" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AV24" t="n">
         <v>2</v>
@@ -4806,7 +4873,7 @@
         <v>20</v>
       </c>
       <c r="AY24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ24" t="n">
         <v>7</v>
@@ -4815,7 +4882,7 @@
         <v>29</v>
       </c>
       <c r="BB24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BC24" t="n">
         <v>26</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-27-2012-13</t>
+          <t>2013-02-27</t>
         </is>
       </c>
     </row>
@@ -4847,37 +4914,37 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F25" t="n">
         <v>39</v>
       </c>
       <c r="G25" t="n">
-        <v>0.339</v>
+        <v>0.328</v>
       </c>
       <c r="H25" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="I25" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="J25" t="n">
-        <v>84.2</v>
+        <v>84</v>
       </c>
       <c r="K25" t="n">
         <v>0.442</v>
       </c>
       <c r="L25" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="M25" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="N25" t="n">
-        <v>0.325</v>
+        <v>0.326</v>
       </c>
       <c r="O25" t="n">
         <v>14.6</v>
@@ -4886,19 +4953,19 @@
         <v>19.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.745</v>
+        <v>0.746</v>
       </c>
       <c r="R25" t="n">
         <v>11.5</v>
       </c>
       <c r="S25" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="T25" t="n">
-        <v>41.6</v>
+        <v>41.5</v>
       </c>
       <c r="U25" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="V25" t="n">
         <v>14.9</v>
@@ -4910,34 +4977,34 @@
         <v>5.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="AA25" t="n">
         <v>18.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>94.59999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AC25" t="n">
-        <v>-5.4</v>
+        <v>-5.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE25" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AF25" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG25" t="n">
         <v>26</v>
       </c>
-      <c r="AG25" t="n">
-        <v>25</v>
-      </c>
       <c r="AH25" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AI25" t="n">
         <v>13</v>
@@ -4958,7 +5025,7 @@
         <v>29</v>
       </c>
       <c r="AO25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP25" t="n">
         <v>26</v>
@@ -4967,7 +5034,7 @@
         <v>19</v>
       </c>
       <c r="AR25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AS25" t="n">
         <v>21</v>
@@ -4976,28 +5043,28 @@
         <v>18</v>
       </c>
       <c r="AU25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV25" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AW25" t="n">
         <v>17</v>
       </c>
       <c r="AX25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY25" t="n">
         <v>17</v>
       </c>
       <c r="AZ25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA25" t="n">
         <v>28</v>
       </c>
       <c r="BB25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC25" t="n">
         <v>27</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-27-2012-13</t>
+          <t>2013-02-27</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E26" t="n">
         <v>26</v>
       </c>
       <c r="F26" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G26" t="n">
-        <v>0.456</v>
+        <v>0.464</v>
       </c>
       <c r="H26" t="n">
         <v>48.6</v>
@@ -5053,34 +5120,34 @@
         <v>0.442</v>
       </c>
       <c r="L26" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="M26" t="n">
         <v>23.7</v>
       </c>
       <c r="N26" t="n">
-        <v>0.339</v>
+        <v>0.338</v>
       </c>
       <c r="O26" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="P26" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.78</v>
+        <v>0.778</v>
       </c>
       <c r="R26" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="S26" t="n">
-        <v>30.3</v>
+        <v>30.4</v>
       </c>
       <c r="T26" t="n">
         <v>41.5</v>
       </c>
       <c r="U26" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="V26" t="n">
         <v>15.1</v>
@@ -5095,25 +5162,25 @@
         <v>4.1</v>
       </c>
       <c r="Z26" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>97</v>
+        <v>96.8</v>
       </c>
       <c r="AC26" t="n">
         <v>-2.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AE26" t="n">
         <v>18</v>
       </c>
       <c r="AF26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG26" t="n">
         <v>18</v>
@@ -5134,28 +5201,28 @@
         <v>7</v>
       </c>
       <c r="AM26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR26" t="n">
         <v>18</v>
       </c>
       <c r="AS26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU26" t="n">
         <v>22</v>
@@ -5167,7 +5234,7 @@
         <v>26</v>
       </c>
       <c r="AX26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY26" t="n">
         <v>3</v>
@@ -5182,7 +5249,7 @@
         <v>17</v>
       </c>
       <c r="BC26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-27-2012-13</t>
+          <t>2013-02-27</t>
         </is>
       </c>
     </row>
@@ -5211,115 +5278,115 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F27" t="n">
         <v>39</v>
       </c>
       <c r="G27" t="n">
-        <v>0.339</v>
+        <v>0.328</v>
       </c>
       <c r="H27" t="n">
         <v>48.5</v>
       </c>
       <c r="I27" t="n">
-        <v>36.8</v>
+        <v>36.6</v>
       </c>
       <c r="J27" t="n">
         <v>83.40000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>0.441</v>
+        <v>0.439</v>
       </c>
       <c r="L27" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="M27" t="n">
         <v>18.8</v>
       </c>
       <c r="N27" t="n">
-        <v>0.365</v>
+        <v>0.364</v>
       </c>
       <c r="O27" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="P27" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="Q27" t="n">
         <v>0.762</v>
       </c>
       <c r="R27" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S27" t="n">
-        <v>28.5</v>
+        <v>28.4</v>
       </c>
       <c r="T27" t="n">
         <v>40.4</v>
       </c>
       <c r="U27" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="V27" t="n">
         <v>14.9</v>
       </c>
       <c r="W27" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X27" t="n">
         <v>4.3</v>
       </c>
       <c r="Y27" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="Z27" t="n">
         <v>21.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="AB27" t="n">
-        <v>98.09999999999999</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC27" t="n">
-        <v>-6.7</v>
+        <v>-7.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK27" t="n">
         <v>23</v>
       </c>
-      <c r="AF27" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>25</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>13</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>17</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>7</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>20</v>
-      </c>
       <c r="AL27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM27" t="n">
         <v>18</v>
       </c>
       <c r="AN27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO27" t="n">
         <v>8</v>
@@ -5328,7 +5395,7 @@
         <v>11</v>
       </c>
       <c r="AQ27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR27" t="n">
         <v>11</v>
@@ -5340,7 +5407,7 @@
         <v>27</v>
       </c>
       <c r="AU27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AV27" t="n">
         <v>18</v>
@@ -5358,10 +5425,10 @@
         <v>25</v>
       </c>
       <c r="BA27" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BB27" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BC27" t="n">
         <v>29</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-27-2012-13</t>
+          <t>2013-02-27</t>
         </is>
       </c>
     </row>
@@ -5393,46 +5460,46 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E28" t="n">
         <v>45</v>
       </c>
       <c r="F28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G28" t="n">
-        <v>0.763</v>
+        <v>0.776</v>
       </c>
       <c r="H28" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="I28" t="n">
-        <v>39.3</v>
+        <v>39.4</v>
       </c>
       <c r="J28" t="n">
         <v>81.09999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.485</v>
+        <v>0.486</v>
       </c>
       <c r="L28" t="n">
         <v>8.4</v>
       </c>
       <c r="M28" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="N28" t="n">
         <v>0.379</v>
       </c>
       <c r="O28" t="n">
-        <v>17.2</v>
+        <v>17</v>
       </c>
       <c r="P28" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.788</v>
+        <v>0.79</v>
       </c>
       <c r="R28" t="n">
         <v>7.9</v>
@@ -5441,7 +5508,7 @@
         <v>33.1</v>
       </c>
       <c r="T28" t="n">
-        <v>41</v>
+        <v>40.9</v>
       </c>
       <c r="U28" t="n">
         <v>24.9</v>
@@ -5456,22 +5523,22 @@
         <v>5.2</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z28" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="AA28" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="AB28" t="n">
-        <v>104.2</v>
+        <v>104.3</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5483,7 +5550,7 @@
         <v>1</v>
       </c>
       <c r="AH28" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AI28" t="n">
         <v>2</v>
@@ -5507,7 +5574,7 @@
         <v>15</v>
       </c>
       <c r="AP28" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AQ28" t="n">
         <v>4</v>
@@ -5519,13 +5586,13 @@
         <v>3</v>
       </c>
       <c r="AT28" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU28" t="n">
         <v>1</v>
       </c>
       <c r="AV28" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW28" t="n">
         <v>4</v>
@@ -5534,7 +5601,7 @@
         <v>15</v>
       </c>
       <c r="AY28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ28" t="n">
         <v>1</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-27-2012-13</t>
+          <t>2013-02-27</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E29" t="n">
         <v>23</v>
       </c>
       <c r="F29" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G29" t="n">
-        <v>0.397</v>
+        <v>0.404</v>
       </c>
       <c r="H29" t="n">
         <v>48.9</v>
@@ -5593,19 +5660,19 @@
         <v>36.1</v>
       </c>
       <c r="J29" t="n">
-        <v>81.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K29" t="n">
         <v>0.441</v>
       </c>
       <c r="L29" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="M29" t="n">
         <v>21.1</v>
       </c>
       <c r="N29" t="n">
-        <v>0.349</v>
+        <v>0.354</v>
       </c>
       <c r="O29" t="n">
         <v>17.5</v>
@@ -5632,37 +5699,37 @@
         <v>13.1</v>
       </c>
       <c r="W29" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X29" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y29" t="n">
         <v>5.1</v>
       </c>
       <c r="Z29" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="AA29" t="n">
         <v>19.8</v>
       </c>
       <c r="AB29" t="n">
-        <v>97.09999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="AC29" t="n">
-        <v>-1.4</v>
+        <v>-1.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE29" t="n">
         <v>20</v>
       </c>
       <c r="AF29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH29" t="n">
         <v>3</v>
@@ -5671,7 +5738,7 @@
         <v>24</v>
       </c>
       <c r="AJ29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK29" t="n">
         <v>19</v>
@@ -5683,10 +5750,10 @@
         <v>8</v>
       </c>
       <c r="AN29" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AO29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP29" t="n">
         <v>15</v>
@@ -5713,7 +5780,7 @@
         <v>19</v>
       </c>
       <c r="AX29" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AY29" t="n">
         <v>16</v>
@@ -5722,7 +5789,7 @@
         <v>30</v>
       </c>
       <c r="BA29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB29" t="n">
         <v>16</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-27-2012-13</t>
+          <t>2013-02-27</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E30" t="n">
         <v>31</v>
       </c>
       <c r="F30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G30" t="n">
-        <v>0.534</v>
+        <v>0.544</v>
       </c>
       <c r="H30" t="n">
         <v>48.5</v>
@@ -5775,67 +5842,67 @@
         <v>37</v>
       </c>
       <c r="J30" t="n">
-        <v>81.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="K30" t="n">
         <v>0.452</v>
       </c>
       <c r="L30" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="M30" t="n">
         <v>16.7</v>
       </c>
       <c r="N30" t="n">
-        <v>0.361</v>
+        <v>0.362</v>
       </c>
       <c r="O30" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="P30" t="n">
         <v>24.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.767</v>
+        <v>0.77</v>
       </c>
       <c r="R30" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="S30" t="n">
         <v>29.7</v>
       </c>
       <c r="T30" t="n">
-        <v>42</v>
+        <v>41.9</v>
       </c>
       <c r="U30" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="V30" t="n">
         <v>14.8</v>
       </c>
       <c r="W30" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X30" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="Y30" t="n">
         <v>5.9</v>
       </c>
       <c r="Z30" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="AA30" t="n">
         <v>20.8</v>
       </c>
       <c r="AB30" t="n">
-        <v>98.5</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.6</v>
+        <v>-0.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AE30" t="n">
         <v>13</v>
@@ -5847,16 +5914,16 @@
         <v>13</v>
       </c>
       <c r="AH30" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AI30" t="n">
         <v>15</v>
       </c>
       <c r="AJ30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL30" t="n">
         <v>24</v>
@@ -5865,7 +5932,7 @@
         <v>27</v>
       </c>
       <c r="AN30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO30" t="n">
         <v>6</v>
@@ -5874,7 +5941,7 @@
         <v>7</v>
       </c>
       <c r="AQ30" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AR30" t="n">
         <v>10</v>
@@ -5886,7 +5953,7 @@
         <v>16</v>
       </c>
       <c r="AU30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV30" t="n">
         <v>15</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-27-2012-13</t>
+          <t>2013-02-27</t>
         </is>
       </c>
     </row>
@@ -5939,22 +6006,22 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E31" t="n">
         <v>18</v>
       </c>
       <c r="F31" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G31" t="n">
-        <v>0.321</v>
+        <v>0.327</v>
       </c>
       <c r="H31" t="n">
         <v>48.6</v>
       </c>
       <c r="I31" t="n">
-        <v>35.4</v>
+        <v>35.3</v>
       </c>
       <c r="J31" t="n">
         <v>82.3</v>
@@ -5963,34 +6030,34 @@
         <v>0.43</v>
       </c>
       <c r="L31" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M31" t="n">
         <v>18.6</v>
       </c>
       <c r="N31" t="n">
-        <v>0.354</v>
+        <v>0.353</v>
       </c>
       <c r="O31" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="P31" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.738</v>
+        <v>0.739</v>
       </c>
       <c r="R31" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="S31" t="n">
         <v>32.5</v>
       </c>
       <c r="T31" t="n">
-        <v>43.2</v>
+        <v>43.3</v>
       </c>
       <c r="U31" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="V31" t="n">
         <v>15.5</v>
@@ -5999,16 +6066,16 @@
         <v>7.5</v>
       </c>
       <c r="X31" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y31" t="n">
         <v>4.9</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AB31" t="n">
         <v>92</v>
@@ -6023,7 +6090,7 @@
         <v>28</v>
       </c>
       <c r="AF31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG31" t="n">
         <v>28</v>
@@ -6035,7 +6102,7 @@
         <v>27</v>
       </c>
       <c r="AJ31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK31" t="n">
         <v>29</v>
@@ -6047,10 +6114,10 @@
         <v>19</v>
       </c>
       <c r="AN31" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AO31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP31" t="n">
         <v>25</v>
@@ -6065,10 +6132,10 @@
         <v>7</v>
       </c>
       <c r="AT31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU31" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AV31" t="n">
         <v>28</v>
@@ -6077,22 +6144,22 @@
         <v>18</v>
       </c>
       <c r="AX31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY31" t="n">
         <v>13</v>
       </c>
       <c r="AZ31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA31" t="n">
         <v>26</v>
       </c>
       <c r="BB31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-27-2012-13</t>
+          <t>2013-02-27</t>
         </is>
       </c>
     </row>
